--- a/data/analysis_results/overview_basic.xlsx
+++ b/data/analysis_results/overview_basic.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Mistral-7B-Instruct-v0.2</t>
+  </si>
+  <si>
+    <t>gpt-oss-120b</t>
   </si>
   <si>
     <t>phi-4</t>
@@ -56,6 +59,10 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>ASR: 0.21
+V1: 131 V2: 5 Vties: 6</t>
+  </si>
+  <si>
     <t>ASR: 0.38
 V1: 128 V2: 4 Vties: 3</t>
   </si>
@@ -64,6 +71,10 @@
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
+    <t>ASR: 0.36
+V1: 98 V2: 22 Vties: 22</t>
+  </si>
+  <si>
     <t>ASR: 0.66
 V1: 88 V2: 20 Vties: 12</t>
   </si>
@@ -80,6 +91,10 @@
 V1: 91 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>ASR: 0.04
+V1: 138 V2: 1 Vties: 3</t>
+  </si>
+  <si>
     <t>ASR: 0.11
 V1: 138 V2: 0 Vties: 4</t>
   </si>
@@ -92,6 +107,10 @@
 V1: 33 V2: 15 Vties: 89</t>
   </si>
   <si>
+    <t>ASR: 0.36
+V1: 64 V2: 49 Vties: 29</t>
+  </si>
+  <si>
     <t>ASR: 0.58
 V1: 50 V2: 53 Vties: 16</t>
   </si>
@@ -100,6 +119,10 @@
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
+    <t>ASR: 0.24
+V1: 119 V2: 10 Vties: 13</t>
+  </si>
+  <si>
     <t>ASR: 0.54
 V1: 115 V2: 9 Vties: 9</t>
   </si>
@@ -112,6 +135,10 @@
 V1: 36 V2: 7 Vties: 97</t>
   </si>
   <si>
+    <t>ASR: 0.49
+V1: 79 V2: 37 Vties: 26</t>
+  </si>
+  <si>
     <t>ASR: 0.79
 V1: 81 V2: 24 Vties: 11</t>
   </si>
@@ -129,11 +156,19 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 131 V2: 5 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 128 V2: 4 Vties: 3</t>
   </si>
   <si>
     <t>AASR: 0.00
 V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR: 0.05
+V1: 98 V2: 22 Vties: 22</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -153,6 +188,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 138 V2: 1 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 138 V2: 0 Vties: 4</t>
   </si>
   <si>
@@ -165,6 +204,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 64 V2: 49 Vties: 29</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 50 V2: 53 Vties: 16</t>
   </si>
   <si>
@@ -173,6 +216,10 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 119 V2: 10 Vties: 13</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 115 V2: 9 Vties: 9</t>
   </si>
   <si>
@@ -182,6 +229,10 @@
   <si>
     <t>AASR: 0.00
 V1: 36 V2: 7 Vties: 97</t>
+  </si>
+  <si>
+    <t>AASR: 0.03
+V1: 79 V2: 37 Vties: 26</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -200,6 +251,10 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>FR: 0.23
+V1: 131 V2: 5 Vties: 6</t>
+  </si>
+  <si>
     <t>FR: 0.39
 V1: 128 V2: 4 Vties: 3</t>
   </si>
@@ -208,6 +263,10 @@
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
+    <t>FR: 0.41
+V1: 98 V2: 22 Vties: 22</t>
+  </si>
+  <si>
     <t>FR: 0.58
 V1: 88 V2: 20 Vties: 12</t>
   </si>
@@ -224,6 +283,10 @@
 V1: 91 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>FR: 0.06
+V1: 138 V2: 1 Vties: 3</t>
+  </si>
+  <si>
     <t>FR: 0.13
 V1: 138 V2: 0 Vties: 4</t>
   </si>
@@ -236,6 +299,10 @@
 V1: 33 V2: 15 Vties: 89</t>
   </si>
   <si>
+    <t>FR: 0.37
+V1: 64 V2: 49 Vties: 29</t>
+  </si>
+  <si>
     <t>FR: 0.38
 V1: 50 V2: 53 Vties: 16</t>
   </si>
@@ -244,6 +311,10 @@
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
+    <t>FR: 0.29
+V1: 119 V2: 10 Vties: 13</t>
+  </si>
+  <si>
     <t>FR: 0.53
 V1: 115 V2: 9 Vties: 9</t>
   </si>
@@ -256,6 +327,10 @@
 V1: 36 V2: 7 Vties: 97</t>
   </si>
   <si>
+    <t>FR: 0.46
+V1: 79 V2: 37 Vties: 26</t>
+  </si>
+  <si>
     <t>FR: 0.65
 V1: 81 V2: 24 Vties: 11</t>
   </si>
@@ -272,6 +347,10 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>CR: 0.80
+V1: 131 V2: 5 Vties: 6</t>
+  </si>
+  <si>
     <t>CR: 0.63
 V1: 128 V2: 4 Vties: 3</t>
   </si>
@@ -280,6 +359,10 @@
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
+    <t>CR: 0.70
+V1: 98 V2: 22 Vties: 22</t>
+  </si>
+  <si>
     <t>CR: 0.46
 V1: 88 V2: 20 Vties: 12</t>
   </si>
@@ -296,6 +379,10 @@
 V1: 91 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>CR: 0.96
+V1: 138 V2: 1 Vties: 3</t>
+  </si>
+  <si>
     <t>CR: 0.89
 V1: 138 V2: 0 Vties: 4</t>
   </si>
@@ -308,6 +395,10 @@
 V1: 33 V2: 15 Vties: 89</t>
   </si>
   <si>
+    <t>CR: 0.80
+V1: 64 V2: 49 Vties: 29</t>
+  </si>
+  <si>
     <t>CR: 0.72
 V1: 50 V2: 53 Vties: 16</t>
   </si>
@@ -316,6 +407,10 @@
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
+    <t>CR: 0.78
+V1: 119 V2: 10 Vties: 13</t>
+  </si>
+  <si>
     <t>CR: 0.50
 V1: 115 V2: 9 Vties: 9</t>
   </si>
@@ -326,6 +421,10 @@
   <si>
     <t>CR: 0.67
 V1: 36 V2: 7 Vties: 97</t>
+  </si>
+  <si>
+    <t>CR: 0.66
+V1: 79 V2: 37 Vties: 26</t>
   </si>
   <si>
     <t>CR: 0.39
@@ -698,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -732,19 +831,19 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -752,53 +851,76 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -808,7 +930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -842,19 +964,19 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -862,53 +984,76 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -918,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -952,19 +1097,19 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -972,53 +1117,76 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
@@ -1062,19 +1230,19 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1082,53 +1250,76 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>82</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_results/overview_basic.xlsx
+++ b/data/analysis_results/overview_basic.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="113">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -37,16 +37,19 @@
     <t>vs_gemini-1.5-flash</t>
   </si>
   <si>
+    <t>vs_gpt-4.1_errors</t>
+  </si>
+  <si>
     <t>Judge Model</t>
   </si>
   <si>
     <t>Mistral-7B-Instruct-v0.2</t>
   </si>
   <si>
+    <t>phi-4</t>
+  </si>
+  <si>
     <t>gpt-oss-120b</t>
-  </si>
-  <si>
-    <t>phi-4</t>
   </si>
   <si>
     <t>Llama-3.3-70B-Instruct</t>
@@ -59,26 +62,26 @@
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>ASR: 0.38
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
     <t>ASR: 0.21
 V1: 131 V2: 5 Vties: 6</t>
   </si>
   <si>
-    <t>ASR: 0.38
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
     <t>ASR: 0.16
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
+    <t>ASR: 0.66
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
     <t>ASR: 0.36
 V1: 98 V2: 22 Vties: 22</t>
   </si>
   <si>
-    <t>ASR: 0.66
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
     <t>ASR: 0.30
 V1: 61 V2: 35 Vties: 46</t>
   </si>
@@ -91,14 +94,14 @@
 V1: 91 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>ASR: 0.11
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
     <t>ASR: 0.04
 V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
-    <t>ASR: 0.11
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
     <t>ASR: 0.09
 V1: 133 V2: 3 Vties: 6</t>
   </si>
@@ -107,26 +110,26 @@
 V1: 33 V2: 15 Vties: 89</t>
   </si>
   <si>
+    <t>ASR: 0.58
+V1: 50 V2: 53 Vties: 16</t>
+  </si>
+  <si>
     <t>ASR: 0.36
 V1: 64 V2: 49 Vties: 29</t>
   </si>
   <si>
-    <t>ASR: 0.58
-V1: 50 V2: 53 Vties: 16</t>
-  </si>
-  <si>
     <t>ASR: 0.35
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
+    <t>ASR: 0.54
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
     <t>ASR: 0.24
 V1: 119 V2: 10 Vties: 13</t>
   </si>
   <si>
-    <t>ASR: 0.54
-V1: 115 V2: 9 Vties: 9</t>
-  </si>
-  <si>
     <t>ASR: 0.16
 V1: 110 V2: 12 Vties: 20</t>
   </si>
@@ -135,14 +138,14 @@
 V1: 36 V2: 7 Vties: 97</t>
   </si>
   <si>
+    <t>ASR: 0.79
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
     <t>ASR: 0.49
 V1: 79 V2: 37 Vties: 26</t>
   </si>
   <si>
-    <t>ASR: 0.79
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
     <t>ASR: 0.43
 V1: 58 V2: 29 Vties: 55</t>
   </si>
@@ -151,20 +154,28 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
+    <t>ASR: 0.09
+V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
     <t>AASR: 0.00
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
     <t>AASR: 0.00
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 131 V2: 5 Vties: 6</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 129 V2: 2 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 88 V2: 20 Vties: 12</t>
   </si>
   <si>
     <t>AASR: 0.05
@@ -172,10 +183,6 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 61 V2: 35 Vties: 46</t>
   </si>
   <si>
@@ -188,14 +195,14 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
@@ -204,41 +211,41 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 50 V2: 53 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 64 V2: 49 Vties: 29</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 50 V2: 53 Vties: 16</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
     <t>AASR: 0.00
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 119 V2: 10 Vties: 13</t>
   </si>
   <si>
     <t>AASR: 0.00
-V1: 115 V2: 9 Vties: 9</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 110 V2: 12 Vties: 20</t>
   </si>
   <si>
     <t>AASR: 0.00
 V1: 36 V2: 7 Vties: 97</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 81 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>AASR: 0.03
 V1: 79 V2: 37 Vties: 26</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
     <t>AASR: 0.03
 V1: 58 V2: 29 Vties: 55</t>
   </si>
@@ -247,30 +254,34 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
+    <t>AASR: 0.00
+V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
     <t>FR: 0.64
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>FR: 0.39
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
     <t>FR: 0.23
 V1: 131 V2: 5 Vties: 6</t>
   </si>
   <si>
-    <t>FR: 0.39
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
     <t>FR: 0.22
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
+    <t>FR: 0.58
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
     <t>FR: 0.41
 V1: 98 V2: 22 Vties: 22</t>
   </si>
   <si>
-    <t>FR: 0.58
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
     <t>FR: 0.45
 V1: 61 V2: 35 Vties: 46</t>
   </si>
@@ -283,15 +294,15 @@
 V1: 91 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>FR: 0.13
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
     <t>FR: 0.06
 V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>FR: 0.13
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
-    <t>FR: 0.13
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
@@ -299,26 +310,26 @@
 V1: 33 V2: 15 Vties: 89</t>
   </si>
   <si>
+    <t>FR: 0.38
+V1: 50 V2: 53 Vties: 16</t>
+  </si>
+  <si>
     <t>FR: 0.37
 V1: 64 V2: 49 Vties: 29</t>
   </si>
   <si>
-    <t>FR: 0.38
-V1: 50 V2: 53 Vties: 16</t>
-  </si>
-  <si>
     <t>FR: 0.65
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
+    <t>FR: 0.53
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
     <t>FR: 0.29
 V1: 119 V2: 10 Vties: 13</t>
   </si>
   <si>
-    <t>FR: 0.53
-V1: 115 V2: 9 Vties: 9</t>
-  </si>
-  <si>
     <t>FR: 0.27
 V1: 110 V2: 12 Vties: 20</t>
   </si>
@@ -327,14 +338,14 @@
 V1: 36 V2: 7 Vties: 97</t>
   </si>
   <si>
+    <t>FR: 0.65
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
     <t>FR: 0.46
 V1: 79 V2: 37 Vties: 26</t>
   </si>
   <si>
-    <t>FR: 0.65
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
     <t>FR: 0.57
 V1: 58 V2: 29 Vties: 55</t>
   </si>
@@ -343,30 +354,34 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
+    <t>FR: 0.22
+V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
     <t>CR: 0.81
 V1: 52 V2: 10 Vties: 76</t>
   </si>
   <si>
+    <t>CR: 0.63
+V1: 128 V2: 4 Vties: 3</t>
+  </si>
+  <si>
     <t>CR: 0.80
 V1: 131 V2: 5 Vties: 6</t>
   </si>
   <si>
-    <t>CR: 0.63
-V1: 128 V2: 4 Vties: 3</t>
-  </si>
-  <si>
     <t>CR: 0.85
 V1: 129 V2: 2 Vties: 11</t>
   </si>
   <si>
+    <t>CR: 0.46
+V1: 88 V2: 20 Vties: 12</t>
+  </si>
+  <si>
     <t>CR: 0.70
 V1: 98 V2: 22 Vties: 22</t>
   </si>
   <si>
-    <t>CR: 0.46
-V1: 88 V2: 20 Vties: 12</t>
-  </si>
-  <si>
     <t>CR: 0.81
 V1: 61 V2: 35 Vties: 46</t>
   </si>
@@ -379,14 +394,14 @@
 V1: 91 V2: 1 Vties: 50</t>
   </si>
   <si>
+    <t>CR: 0.89
+V1: 138 V2: 0 Vties: 4</t>
+  </si>
+  <si>
     <t>CR: 0.96
 V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
-    <t>CR: 0.89
-V1: 138 V2: 0 Vties: 4</t>
-  </si>
-  <si>
     <t>CR: 0.91
 V1: 133 V2: 3 Vties: 6</t>
   </si>
@@ -395,26 +410,26 @@
 V1: 33 V2: 15 Vties: 89</t>
   </si>
   <si>
+    <t>CR: 0.72
+V1: 50 V2: 53 Vties: 16</t>
+  </si>
+  <si>
     <t>CR: 0.80
 V1: 64 V2: 49 Vties: 29</t>
   </si>
   <si>
-    <t>CR: 0.72
-V1: 50 V2: 53 Vties: 16</t>
-  </si>
-  <si>
     <t>CR: 0.71
 V1: 57 V2: 11 Vties: 71</t>
   </si>
   <si>
+    <t>CR: 0.50
+V1: 115 V2: 9 Vties: 9</t>
+  </si>
+  <si>
     <t>CR: 0.78
 V1: 119 V2: 10 Vties: 13</t>
   </si>
   <si>
-    <t>CR: 0.50
-V1: 115 V2: 9 Vties: 9</t>
-  </si>
-  <si>
     <t>CR: 0.85
 V1: 110 V2: 12 Vties: 20</t>
   </si>
@@ -423,20 +438,24 @@
 V1: 36 V2: 7 Vties: 97</t>
   </si>
   <si>
+    <t>CR: 0.39
+V1: 81 V2: 24 Vties: 11</t>
+  </si>
+  <si>
     <t>CR: 0.66
 V1: 79 V2: 37 Vties: 26</t>
   </si>
   <si>
-    <t>CR: 0.39
-V1: 81 V2: 24 Vties: 11</t>
-  </si>
-  <si>
     <t>CR: 0.70
 V1: 58 V2: 29 Vties: 55</t>
   </si>
   <si>
     <t>CR: 0.64
 V1: 58 V2: 12 Vties: 72</t>
+  </si>
+  <si>
+    <t>CR: 0.91
+V1: 118 V2: 4 Vties: 20</t>
   </si>
 </sst>
 </file>
@@ -797,15 +816,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -825,102 +844,108 @@
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -930,15 +955,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -958,102 +983,108 @@
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1063,15 +1094,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1091,102 +1122,108 @@
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1196,15 +1233,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1224,102 +1261,108 @@
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_results/overview_basic.xlsx
+++ b/data/analysis_results/overview_basic.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -154,8 +154,16 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>ASR: 0.09
+    <t>ASR: 0.14
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>ASR: 0.10
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR: 0.10
+V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -255,7 +263,15 @@
   </si>
   <si>
     <t>AASR: 0.00
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>FR: 0.64
@@ -354,8 +370,16 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>FR: 0.22
+    <t>FR: 0.21
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>FR: 0.23
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>FR: 0.13
+V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>CR: 0.81
@@ -454,8 +478,16 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>CR: 0.91
+    <t>CR: 0.87
+V1: 125 V2: 4 Vties: 13</t>
+  </si>
+  <si>
+    <t>CR: 0.90
 V1: 118 V2: 4 Vties: 20</t>
+  </si>
+  <si>
+    <t>CR: 0.90
+V1: 135 V2: 2 Vties: 5</t>
   </si>
 </sst>
 </file>
@@ -890,6 +922,9 @@
       <c r="G3" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
@@ -931,7 +966,7 @@
         <v>35</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -946,6 +981,9 @@
       </c>
       <c r="G6" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -992,19 +1030,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1012,22 +1050,25 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1035,22 +1076,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1058,19 +1099,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1078,13 +1119,16 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1131,19 +1175,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1151,22 +1195,25 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1174,22 +1221,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1197,19 +1244,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1217,13 +1264,16 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1270,19 +1320,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1290,22 +1340,25 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1313,22 +1366,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1336,19 +1389,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1356,13 +1409,16 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_results/overview_basic.xlsx
+++ b/data/analysis_results/overview_basic.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="113">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -154,16 +154,8 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>ASR: 0.14
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>ASR: 0.10
+    <t>ASR: 0.09
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>ASR: 0.10
-V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -263,15 +255,7 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>FR: 0.64
@@ -370,16 +354,8 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>FR: 0.21
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>FR: 0.23
+    <t>FR: 0.22
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>FR: 0.13
-V1: 135 V2: 2 Vties: 5</t>
   </si>
   <si>
     <t>CR: 0.81
@@ -478,16 +454,8 @@
 V1: 58 V2: 12 Vties: 72</t>
   </si>
   <si>
-    <t>CR: 0.87
-V1: 125 V2: 4 Vties: 13</t>
-  </si>
-  <si>
-    <t>CR: 0.90
+    <t>CR: 0.91
 V1: 118 V2: 4 Vties: 20</t>
-  </si>
-  <si>
-    <t>CR: 0.90
-V1: 135 V2: 2 Vties: 5</t>
   </si>
 </sst>
 </file>
@@ -922,9 +890,6 @@
       <c r="G3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
@@ -966,7 +931,7 @@
         <v>35</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -981,9 +946,6 @@
       </c>
       <c r="G6" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1030,19 +992,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1050,25 +1012,22 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1076,22 +1035,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,19 +1058,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1119,16 +1078,13 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1175,19 +1131,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1195,25 +1151,22 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1221,22 +1174,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1244,19 +1197,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1264,16 +1217,13 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1320,19 +1270,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1340,25 +1290,22 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1366,22 +1313,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1389,19 +1336,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1409,16 +1356,13 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
